--- a/Pagos_Meta.xlsx
+++ b/Pagos_Meta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Downloads\dashboard-kit-maste2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Downloads\dashboard-kit-maste2\DASHBOARD_VENTAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E13474AE-E728-4C6E-B60C-DEF605FD7E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7713B0D-F041-47F7-9753-556C677A28D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2061,7 +2061,7 @@
         <v>45740</v>
       </c>
       <c r="B206">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
@@ -2069,7 +2069,7 @@
         <v>45741</v>
       </c>
       <c r="B207">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
@@ -2077,7 +2077,7 @@
         <v>45742</v>
       </c>
       <c r="B208">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
@@ -2085,7 +2085,7 @@
         <v>45743</v>
       </c>
       <c r="B209">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
@@ -2093,7 +2093,7 @@
         <v>45744</v>
       </c>
       <c r="B210">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
@@ -2101,7 +2101,7 @@
         <v>45745</v>
       </c>
       <c r="B211">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">

--- a/Pagos_Meta.xlsx
+++ b/Pagos_Meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Downloads\dashboard-kit-maste2\DASHBOARD_VENTAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7713B0D-F041-47F7-9753-556C677A28D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694F41A5-6ADE-45BC-860E-D0D75E1C1AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2117,7 +2117,7 @@
         <v>45747</v>
       </c>
       <c r="B213">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
@@ -2125,7 +2125,7 @@
         <v>45748</v>
       </c>
       <c r="B214">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
@@ -2157,7 +2157,7 @@
         <v>45752</v>
       </c>
       <c r="B218">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">

--- a/Pagos_Meta.xlsx
+++ b/Pagos_Meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Downloads\dashboard-kit-maste2\DASHBOARD_VENTAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694F41A5-6ADE-45BC-860E-D0D75E1C1AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0080C60C-910F-450C-8A07-CD049DA03E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64B69AB-9461-4242-80D9-B02C7652336F}">
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -426,215 +428,215 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>45536</v>
+        <v>45752</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>45537</v>
+        <v>45753</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>45538</v>
+        <v>45754</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>45539</v>
+        <v>45755</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>45540</v>
+        <v>45756</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>45541</v>
+        <v>45757</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>45542</v>
+        <v>45758</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>45543</v>
+        <v>45759</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>45544</v>
+        <v>45760</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>45545</v>
+        <v>45761</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>45546</v>
+        <v>45762</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>45547</v>
+        <v>45763</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>45548</v>
+        <v>45764</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>45549</v>
+        <v>45765</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>45550</v>
+        <v>45766</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>45551</v>
+        <v>45767</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>45552</v>
+        <v>45768</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>45553</v>
+        <v>45769</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>45554</v>
+        <v>45770</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>45555</v>
+        <v>45771</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>45556</v>
+        <v>45772</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>45557</v>
+        <v>45773</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>45558</v>
+        <v>45774</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>45559</v>
+        <v>45775</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>45560</v>
+        <v>45776</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>45561</v>
+        <v>45777</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>45562</v>
+        <v>45778</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -642,7 +644,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>45563</v>
+        <v>45779</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -650,15 +652,15 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>45564</v>
+        <v>45780</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>45565</v>
+        <v>45781</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -666,255 +668,255 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>45566</v>
+        <v>45782</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>45567</v>
+        <v>45783</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>45568</v>
+        <v>45784</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>45569</v>
+        <v>45785</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>45570</v>
+        <v>45786</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>45571</v>
+        <v>45787</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>45572</v>
+        <v>45788</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>45573</v>
+        <v>45789</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>45574</v>
+        <v>45790</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>45575</v>
+        <v>45791</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>45576</v>
+        <v>45792</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>45577</v>
+        <v>45793</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>45578</v>
+        <v>45794</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>45579</v>
+        <v>45795</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>45580</v>
+        <v>45796</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>45581</v>
+        <v>45797</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>45582</v>
+        <v>45798</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>45583</v>
+        <v>45799</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>45584</v>
+        <v>45800</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>45585</v>
+        <v>45801</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>45586</v>
+        <v>45802</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>45587</v>
+        <v>45803</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>45588</v>
+        <v>45804</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>45589</v>
+        <v>45805</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>45590</v>
+        <v>45806</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>45591</v>
+        <v>45807</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>45592</v>
+        <v>45808</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>45593</v>
+        <v>45809</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>45594</v>
+        <v>45810</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>45595</v>
+        <v>45811</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>45596</v>
+        <v>45812</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>45597</v>
+        <v>45813</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -922,7 +924,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>45598</v>
+        <v>45814</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -930,15 +932,15 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>45599</v>
+        <v>45815</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>45600</v>
+        <v>45816</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -946,7 +948,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>45601</v>
+        <v>45817</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -954,7 +956,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>45602</v>
+        <v>45818</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -962,7 +964,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>45603</v>
+        <v>45819</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -970,7 +972,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>45604</v>
+        <v>45820</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -978,7 +980,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>45605</v>
+        <v>45821</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -986,15 +988,15 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>45606</v>
+        <v>45822</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>45607</v>
+        <v>45823</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1002,7 +1004,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>45608</v>
+        <v>45824</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -1010,7 +1012,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>45609</v>
+        <v>45825</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -1018,7 +1020,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>45610</v>
+        <v>45826</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1026,7 +1028,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <v>45611</v>
+        <v>45827</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1034,7 +1036,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>45612</v>
+        <v>45828</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1042,15 +1044,15 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>45613</v>
+        <v>45829</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>45614</v>
+        <v>45830</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1058,7 +1060,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>45615</v>
+        <v>45831</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1066,7 +1068,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <v>45616</v>
+        <v>45832</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1074,7 +1076,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <v>45617</v>
+        <v>45833</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -1082,7 +1084,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <v>45618</v>
+        <v>45834</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1090,7 +1092,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <v>45619</v>
+        <v>45835</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -1098,15 +1100,15 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <v>45620</v>
+        <v>45836</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>45621</v>
+        <v>45837</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1114,7 +1116,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>45622</v>
+        <v>45838</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1122,47 +1124,47 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>45623</v>
+        <v>45839</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <v>45624</v>
+        <v>45840</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>45625</v>
+        <v>45841</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <v>45626</v>
+        <v>45842</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <v>45627</v>
+        <v>45843</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <v>45628</v>
+        <v>45844</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -1170,7 +1172,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <v>45629</v>
+        <v>45845</v>
       </c>
       <c r="B95">
         <v>3</v>
@@ -1178,7 +1180,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <v>45630</v>
+        <v>45846</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -1186,7 +1188,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <v>45631</v>
+        <v>45847</v>
       </c>
       <c r="B97">
         <v>3</v>
@@ -1194,7 +1196,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>45632</v>
+        <v>45848</v>
       </c>
       <c r="B98">
         <v>3</v>
@@ -1202,7 +1204,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <v>45633</v>
+        <v>45849</v>
       </c>
       <c r="B99">
         <v>3</v>
@@ -1210,15 +1212,15 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <v>45634</v>
+        <v>45850</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>45635</v>
+        <v>45851</v>
       </c>
       <c r="B101">
         <v>3</v>
@@ -1226,7 +1228,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>45636</v>
+        <v>45852</v>
       </c>
       <c r="B102">
         <v>3</v>
@@ -1234,7 +1236,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
-        <v>45637</v>
+        <v>45853</v>
       </c>
       <c r="B103">
         <v>3</v>
@@ -1242,7 +1244,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <v>45638</v>
+        <v>45854</v>
       </c>
       <c r="B104">
         <v>3</v>
@@ -1250,7 +1252,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <v>45639</v>
+        <v>45855</v>
       </c>
       <c r="B105">
         <v>3</v>
@@ -1258,7 +1260,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
-        <v>45640</v>
+        <v>45856</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -1266,15 +1268,15 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <v>45641</v>
+        <v>45857</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <v>45642</v>
+        <v>45858</v>
       </c>
       <c r="B108">
         <v>3</v>
@@ -1282,7 +1284,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <v>45643</v>
+        <v>45859</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -1290,7 +1292,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>45644</v>
+        <v>45860</v>
       </c>
       <c r="B110">
         <v>3</v>
@@ -1298,7 +1300,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>45645</v>
+        <v>45861</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -1306,7 +1308,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <v>45646</v>
+        <v>45862</v>
       </c>
       <c r="B112">
         <v>3</v>
@@ -1314,7 +1316,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
-        <v>45647</v>
+        <v>45863</v>
       </c>
       <c r="B113">
         <v>3</v>
@@ -1322,15 +1324,15 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <v>45648</v>
+        <v>45864</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <v>45649</v>
+        <v>45865</v>
       </c>
       <c r="B115">
         <v>3</v>
@@ -1338,7 +1340,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <v>45650</v>
+        <v>45866</v>
       </c>
       <c r="B116">
         <v>3</v>
@@ -1346,7 +1348,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <v>45651</v>
+        <v>45867</v>
       </c>
       <c r="B117">
         <v>3</v>
@@ -1354,7 +1356,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <v>45652</v>
+        <v>45868</v>
       </c>
       <c r="B118">
         <v>3</v>
@@ -1362,7 +1364,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>45653</v>
+        <v>45869</v>
       </c>
       <c r="B119">
         <v>3</v>
@@ -1370,809 +1372,249 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>45654</v>
+        <v>45870</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <v>45655</v>
+        <v>45871</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <v>45656</v>
+        <v>45872</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>45657</v>
+        <v>45873</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>45658</v>
+        <v>45874</v>
       </c>
       <c r="B124">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>45659</v>
+        <v>45875</v>
       </c>
       <c r="B125">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <v>45660</v>
+        <v>45876</v>
       </c>
       <c r="B126">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>45661</v>
+        <v>45877</v>
       </c>
       <c r="B127">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>45662</v>
+        <v>45878</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
-        <v>45663</v>
+        <v>45879</v>
       </c>
       <c r="B129">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
-        <v>45664</v>
+        <v>45880</v>
       </c>
       <c r="B130">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
-        <v>45665</v>
+        <v>45881</v>
       </c>
       <c r="B131">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
-        <v>45666</v>
+        <v>45882</v>
       </c>
       <c r="B132">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
-        <v>45667</v>
+        <v>45883</v>
       </c>
       <c r="B133">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
-        <v>45668</v>
+        <v>45884</v>
       </c>
       <c r="B134">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
-        <v>45669</v>
+        <v>45885</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
-        <v>45670</v>
+        <v>45886</v>
       </c>
       <c r="B136">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
-        <v>45671</v>
+        <v>45887</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
-        <v>45672</v>
+        <v>45888</v>
       </c>
       <c r="B138">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
-        <v>45673</v>
+        <v>45889</v>
       </c>
       <c r="B139">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
-        <v>45674</v>
+        <v>45890</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
-        <v>45675</v>
+        <v>45891</v>
       </c>
       <c r="B141">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
-        <v>45676</v>
+        <v>45892</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
-        <v>45677</v>
+        <v>45893</v>
       </c>
       <c r="B143">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
-        <v>45678</v>
+        <v>45894</v>
       </c>
       <c r="B144">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
-        <v>45679</v>
+        <v>45895</v>
       </c>
       <c r="B145">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>45680</v>
+        <v>45896</v>
       </c>
       <c r="B146">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>45681</v>
+        <v>45897</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>45682</v>
+        <v>45898</v>
       </c>
       <c r="B148">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>45683</v>
+        <v>45899</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>45684</v>
+        <v>45900</v>
       </c>
       <c r="B150">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
-        <v>45685</v>
-      </c>
-      <c r="B151">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="1">
-        <v>45686</v>
-      </c>
-      <c r="B152">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="1">
-        <v>45687</v>
-      </c>
-      <c r="B153">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" s="1">
-        <v>45688</v>
-      </c>
-      <c r="B154">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155" s="1">
-        <v>45689</v>
-      </c>
-      <c r="B155">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
-        <v>45690</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157" s="1">
-        <v>45691</v>
-      </c>
-      <c r="B157">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="1">
-        <v>45692</v>
-      </c>
-      <c r="B158">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="1">
-        <v>45693</v>
-      </c>
-      <c r="B159">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" s="1">
-        <v>45694</v>
-      </c>
-      <c r="B160">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="1">
-        <v>45695</v>
-      </c>
-      <c r="B161">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="1">
-        <v>45696</v>
-      </c>
-      <c r="B162">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="1">
-        <v>45697</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
-        <v>45698</v>
-      </c>
-      <c r="B164">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="1">
-        <v>45699</v>
-      </c>
-      <c r="B165">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="1">
-        <v>45700</v>
-      </c>
-      <c r="B166">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="1">
-        <v>45701</v>
-      </c>
-      <c r="B167">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="1">
-        <v>45702</v>
-      </c>
-      <c r="B168">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="1">
-        <v>45703</v>
-      </c>
-      <c r="B169">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="1">
-        <v>45704</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="1">
-        <v>45705</v>
-      </c>
-      <c r="B171">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="1">
-        <v>45706</v>
-      </c>
-      <c r="B172">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173" s="1">
-        <v>45707</v>
-      </c>
-      <c r="B173">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="1">
-        <v>45708</v>
-      </c>
-      <c r="B174">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="1">
-        <v>45709</v>
-      </c>
-      <c r="B175">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="1">
-        <v>45710</v>
-      </c>
-      <c r="B176">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="1">
-        <v>45711</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="1">
-        <v>45712</v>
-      </c>
-      <c r="B178">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="1">
-        <v>45713</v>
-      </c>
-      <c r="B179">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="1">
-        <v>45714</v>
-      </c>
-      <c r="B180">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="1">
-        <v>45715</v>
-      </c>
-      <c r="B181">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="1">
-        <v>45716</v>
-      </c>
-      <c r="B182">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="1">
-        <v>45717</v>
-      </c>
-      <c r="B183">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="1">
-        <v>45718</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="1">
-        <v>45719</v>
-      </c>
-      <c r="B185">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="1">
-        <v>45720</v>
-      </c>
-      <c r="B186">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="1">
-        <v>45721</v>
-      </c>
-      <c r="B187">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="1">
-        <v>45722</v>
-      </c>
-      <c r="B188">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="1">
-        <v>45723</v>
-      </c>
-      <c r="B189">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="1">
-        <v>45724</v>
-      </c>
-      <c r="B190">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="1">
-        <v>45725</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="1">
-        <v>45726</v>
-      </c>
-      <c r="B192">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="1">
-        <v>45727</v>
-      </c>
-      <c r="B193">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="1">
-        <v>45728</v>
-      </c>
-      <c r="B194">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="1">
-        <v>45729</v>
-      </c>
-      <c r="B195">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="1">
-        <v>45730</v>
-      </c>
-      <c r="B196">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="1">
-        <v>45731</v>
-      </c>
-      <c r="B197">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="1">
-        <v>45732</v>
-      </c>
-      <c r="B198">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="1">
-        <v>45733</v>
-      </c>
-      <c r="B199">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="1">
-        <v>45734</v>
-      </c>
-      <c r="B200">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" s="1">
-        <v>45735</v>
-      </c>
-      <c r="B201">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="1">
-        <v>45736</v>
-      </c>
-      <c r="B202">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" s="1">
-        <v>45737</v>
-      </c>
-      <c r="B203">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" s="1">
-        <v>45738</v>
-      </c>
-      <c r="B204">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="1">
-        <v>45739</v>
-      </c>
-      <c r="B205">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="1">
-        <v>45740</v>
-      </c>
-      <c r="B206">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="1">
-        <v>45741</v>
-      </c>
-      <c r="B207">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" s="1">
-        <v>45742</v>
-      </c>
-      <c r="B208">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209" s="1">
-        <v>45743</v>
-      </c>
-      <c r="B209">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A210" s="1">
-        <v>45744</v>
-      </c>
-      <c r="B210">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" s="1">
-        <v>45745</v>
-      </c>
-      <c r="B211">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A212" s="1">
-        <v>45746</v>
-      </c>
-      <c r="B212">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A213" s="1">
-        <v>45747</v>
-      </c>
-      <c r="B213">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214" s="1">
-        <v>45748</v>
-      </c>
-      <c r="B214">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="1">
-        <v>45749</v>
-      </c>
-      <c r="B215">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A216" s="1">
-        <v>45750</v>
-      </c>
-      <c r="B216">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A217" s="1">
-        <v>45751</v>
-      </c>
-      <c r="B217">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A218" s="1">
-        <v>45752</v>
-      </c>
-      <c r="B218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A219" s="1">
-        <v>45753</v>
-      </c>
-      <c r="B219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A220" s="1">
-        <v>45754</v>
-      </c>
-      <c r="B220">
         <v>2</v>
       </c>
     </row>
